--- a/public/templates/Site-Import-Template.xlsx
+++ b/public/templates/Site-Import-Template.xlsx
@@ -1,58 +1,353 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Sites" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <TitlesOfParts>
+    <vt:vector size="4" baseType="lpstr">
+      <vt:lpstr>Instructions</vt:lpstr>
+      <vt:lpstr>Import Template</vt:lpstr>
+      <vt:lpstr>Sample Data</vt:lpstr>
+      <vt:lpstr>Lookup Lists</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:title>EHS360 Site Import Template</dc:title>
+  <dc:creator>Maitsys Assure</dc:creator>
+  <cp:lastModifiedBy>Maitsys Assure</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-01-01T00:00:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-01-01T00:00:00Z</dcterms:modified>
+</cp:coreProperties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+  <si>
+    <t xml:space="preserve">EHS360 - Site Import Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row = one site. Add up to three site users per row to grant them access to that site as soon as it's created — see the User columns below. Leave the user columns blank to add users later instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to put here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The site's full display name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northstar Manufacturing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The unique KC site code. Rows whose code already matches an existing site are skipped — an import never overwrites an existing site record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC-NSM-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of the approved regions (see the Lookup Lists tab). A region typed here that isn't on that list yet is accepted and added to it automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of the approved business segments (see the Lookup Lists tab). Same rule as Region — a new value is accepted and added automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User 1 Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full name of a site user to grant access to this site as soon as it's created. Leave both User 1 columns blank to add no user here yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grace Okonkwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User 1 Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That user's email address. Required if User 1 Name is filled in — a user missing either value is skipped, not imported partially.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grace.okonkwo@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User 2 Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same pattern, for a second user at this site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User 2 Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required if User 2 Name is filled in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daniel.brooks@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User 3 Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same pattern, for a third user at this site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(leave blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User 3 Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required if User 3 Name is filled in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Important — what this template deliberately leaves out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This template only creates NEW sites and, optionally, grants up to three users access to each one. It never edits an existing site's name, region, or segment — use Sites &gt; Edit for that. A site that needs more than three users at import time can have the rest added afterward from Sites &gt; that site &gt; Add user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row = one site. Fill Site Name, Site Code, Region, and Segment for every site; add up to three users to grant immediate access. See the Instructions tab before filling this in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Code *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Data - Illustrative Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictional example content showing the fill pattern — five sites across different regions and segments, with zero to three site users each. Not real Kimberly-Clark sites. Copy this pattern, replace with real site data, and move rows into the Import Template tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ridgeview Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC-RDG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family Care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Whitfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tom.whitfield@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chidi Okafor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chidi.okafor@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meridian Plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC-MRD-092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asia Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiko Tanaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aiko.tanaka@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fairwind Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC-FWD-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper Creek Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC-CCK-165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latin America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucia Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucia.fernandez@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ravi Deshpande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravi.deshpande@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverline Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC-SVL-284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: a Region or Segment typed directly into the Import Template that isn't listed here yet is accepted automatically and added to this list — you don't need to edit this tab first. Manage the master lists anytime from Administration &gt; Config.</t>
+  </si>
+</sst>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF4F46E5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF565E6C"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFA0A4AD"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.5"/>
+      <color rgb="FF565E6C"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF4F46E5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF565E6C"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF4F46E5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F46E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A1A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,22 +355,84 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DCE3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9DCE3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9DCE3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9DCE3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -150,7 +507,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +541,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +575,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,105 +710,812 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14000" firstSheet="1" activeTab="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Import Template" sheetId="2" r:id="rId2"/>
+    <sheet name="Sample Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Lookup Lists" sheetId="4" r:id="rId4"/>
+  </sheets>
+  <calcPr calcId="191028"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Site name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Site code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Region</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Segment</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Northstar Manufacturing</v>
-      </c>
-      <c r="B2" t="str">
-        <v>KC-NSM-042</v>
-      </c>
-      <c r="C2" t="str">
-        <v>North America</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Family Care</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Example Site Name</v>
-      </c>
-      <c r="B3" t="str">
-        <v>KC-XXX-000</v>
-      </c>
-      <c r="C3" t="str">
-        <v>EMEA</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Professional</v>
-      </c>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="32.1" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="42" customHeight="1">
+      <c r="A5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="42" customHeight="1">
+      <c r="A6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="42" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="42" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="42" customHeight="1">
+      <c r="A9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="42" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="42" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="42" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="42" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" ht="30" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+    </row>
+  </sheetData>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000001}">
+          <x14:formula1>
+            <xm:f>'Lookup Lists'!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>C5:C24</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000002}">
+          <x14:formula1>
+            <xm:f>'Lookup Lists'!$C$2:$C$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>D5:D24</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+    </row>
+  </sheetData>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000001}">
+          <x14:formula1>
+            <xm:f>'Lookup Lists'!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>C5:C9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000002}">
+          <x14:formula1>
+            <xm:f>'Lookup Lists'!$C$2:$C$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>D5:D9</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>